--- a/DAY 1/Sikta Das Test Report.xlsx
+++ b/DAY 1/Sikta Das Test Report.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51585ef60b1564a3/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="8_{92144F2E-DF3F-4745-BED5-01A5FD07D8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B65437F0-6FD7-4EA8-964D-C6C0C4666FBD}"/>
+  <xr:revisionPtr revIDLastSave="1247" documentId="8_{92144F2E-DF3F-4745-BED5-01A5FD07D8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E7E552-C4C9-4E77-BC7C-D7B4F22F8051}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{7B3C1056-961D-49EA-8C4B-8AA9121ABA2E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="5" xr2:uid="{7B3C1056-961D-49EA-8C4B-8AA9121ABA2E}"/>
   </bookViews>
   <sheets>
     <sheet name="UserStory" sheetId="2" r:id="rId1"/>
     <sheet name="TestScenarios" sheetId="3" r:id="rId2"/>
     <sheet name="TestCases" sheetId="4" r:id="rId3"/>
+    <sheet name="Defect Report" sheetId="5" r:id="rId4"/>
+    <sheet name="RTM" sheetId="6" r:id="rId5"/>
+    <sheet name="Summary" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="391">
   <si>
     <t>Issue Type</t>
   </si>
@@ -95,9 +98,6 @@
     <t>Add an item</t>
   </si>
   <si>
-    <t>Increase/ Decrease quantity</t>
-  </si>
-  <si>
     <t>SubStory 1</t>
   </si>
   <si>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>Edit items for your inventory</t>
-  </si>
-  <si>
-    <t>Recommendation of Add-Ons</t>
   </si>
   <si>
     <t>NoBroker Packers and Movers Module</t>
@@ -193,12 +190,6 @@
     <t>Verify Inventory Management</t>
   </si>
   <si>
-    <t>1. Validate user can add items
-2. Validate user can update item quantity
-3. Validate user can remove items
-4. Validate inventory is mandatory</t>
-  </si>
-  <si>
     <t>Verify Booking Confirmation</t>
   </si>
   <si>
@@ -335,9 +326,6 @@
   </si>
   <si>
     <t>Select Menu option from homepage</t>
-  </si>
-  <si>
-    <t>To validate navigation</t>
   </si>
   <si>
     <t>Verify Navigation to "Packers and Movers" Page</t>
@@ -349,12 +337,6 @@
 4. Packers and Movers page should be displayed</t>
   </si>
   <si>
-    <t>1. Click on Menu  Option
-2. "Packers and Movers" option should be displayed
-3. Click on "Packers and Movers" Option
-4. "Packers and Movers" Page should be displayed</t>
-  </si>
-  <si>
     <t>TC_NoBroker_02</t>
   </si>
   <si>
@@ -381,9 +363,6 @@
     <t xml:space="preserve">Validate user can select valid city </t>
   </si>
   <si>
-    <t>2. Kolkata</t>
-  </si>
-  <si>
     <t>City gets selected</t>
   </si>
   <si>
@@ -396,20 +375,981 @@
     <t xml:space="preserve">Validate user can select invalid city </t>
   </si>
   <si>
-    <t>2. Bhubaneswar</t>
-  </si>
-  <si>
     <t>"No Cities Found" should be shown</t>
   </si>
   <si>
     <t>"No Cities Found" is shown</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid city</t>
+  </si>
+  <si>
+    <t>1. Bhubaneswar</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_03</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate user can enter valid pickup location </t>
+  </si>
+  <si>
+    <t>1. Selected a valid city</t>
+  </si>
+  <si>
+    <t>Pickup Location should be selected</t>
+  </si>
+  <si>
+    <t>Pickup Location is selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate user can enter invalid pickup location </t>
+  </si>
+  <si>
+    <t>1. Enter an invalid pickup location</t>
+  </si>
+  <si>
+    <t>1. dgegu</t>
+  </si>
+  <si>
+    <t>"Please enter your pickup locality"
+ should be displayed</t>
+  </si>
+  <si>
+    <t>"Please enter your pickup locality" 
+is displayed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate user can enter valid drop location </t>
+  </si>
+  <si>
+    <t>1. Enter a valid drop location</t>
+  </si>
+  <si>
+    <t>Drop Location should be selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate user can enter invalid drop location </t>
+  </si>
+  <si>
+    <t>1. Enter an invalid drop location</t>
+  </si>
+  <si>
+    <t>1. csgs</t>
+  </si>
+  <si>
+    <t>"Please enter your destination locality" should be displayed</t>
+  </si>
+  <si>
+    <t>"Please enter your destination 
+locality" is displayed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_06</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_07</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_08</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_09</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_10</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_11</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_12</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_13</t>
+  </si>
+  <si>
+    <t>Validate error for empty/invalid location</t>
+  </si>
+  <si>
+    <t>"This route is currently not 
+serviceable" message is 
+displayed</t>
+  </si>
+  <si>
+    <t>2. Bangalore</t>
+  </si>
+  <si>
+    <t>1. Kolkata
+2. Rajarhat
+3. Newtown</t>
+  </si>
+  <si>
+    <t>1. Select a valid city
+2. Enter no pickup location
+3. Enter no drop location</t>
+  </si>
+  <si>
+    <t>1. Bangalore</t>
+  </si>
+  <si>
+    <t>"Please enter valid locality" message for both the fields should be displayed</t>
+  </si>
+  <si>
+    <t>"Please enter valid locality" message for both the fields is displayed</t>
+  </si>
+  <si>
+    <t>1. Select a valid city
+2. Enter valid pickup location
+3. Enter no drop location</t>
+  </si>
+  <si>
+    <t>1. Select a valid city
+2. Enter no pickup location
+3. Enter valid drop location</t>
+  </si>
+  <si>
+    <t>"Please enter your destination" 
+locality should be displayed</t>
+  </si>
+  <si>
+    <t>"Please enter your destination" 
+locality is displayed</t>
+  </si>
+  <si>
+    <t>"Please enter your pickup locality" 
+should be displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Please enter your pickup locality" 
+is displayed </t>
+  </si>
+  <si>
+    <t>TC_NoBroker_14</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_15</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_16</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_17</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_18</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_19</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_20</t>
+  </si>
+  <si>
+    <t>Validate user can select "within city"</t>
+  </si>
+  <si>
+    <t>1. Selected a valid city
+2. Selected a valid pickup location
+3. Selected a valid drop location</t>
+  </si>
+  <si>
+    <t>1. Select "within city" option</t>
+  </si>
+  <si>
+    <t>1. N/A</t>
+  </si>
+  <si>
+    <t>"within city" option should be selected</t>
+  </si>
+  <si>
+    <t>"within city" option is selected</t>
+  </si>
+  <si>
+    <t>Validate user can select "between cities"</t>
+  </si>
+  <si>
+    <t>1. Select "between cities" option</t>
+  </si>
+  <si>
+    <t>"between cities" option should be selected</t>
+  </si>
+  <si>
+    <t>"between cities" option is selected</t>
+  </si>
+  <si>
+    <t>Validate user can select "vehicle shifting"</t>
+  </si>
+  <si>
+    <t>1. Select "vehicle shifting" option</t>
+  </si>
+  <si>
+    <t>"vehicle shifting" option should be selected</t>
+  </si>
+  <si>
+    <t>"vehicle shifting" option is selected</t>
+  </si>
+  <si>
+    <t>Validate user can add items</t>
+  </si>
+  <si>
+    <t>1. Selected a valid shift</t>
+  </si>
+  <si>
+    <t>Delete an item</t>
+  </si>
+  <si>
+    <t>Update item quantity</t>
+  </si>
+  <si>
+    <t>Sub Story 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate user can search for items </t>
+  </si>
+  <si>
+    <t>1. Click on search box
+2. Enter a valid item
+3. Click Enter</t>
+  </si>
+  <si>
+    <t>2. Bed</t>
+  </si>
+  <si>
+    <t>List of items related to "Bed" should be shown</t>
+  </si>
+  <si>
+    <t>1. Click on search box
+2. Enter an invalid item
+3. Click Enter</t>
+  </si>
+  <si>
+    <t>2. Pen</t>
+  </si>
+  <si>
+    <t>"No items found" message should be displayed</t>
+  </si>
+  <si>
+    <t>List of items related to "Bed" is 
+shown</t>
+  </si>
+  <si>
+    <t>"No items found" message is 
+displayed</t>
+  </si>
+  <si>
+    <t>Item should be added</t>
+  </si>
+  <si>
+    <t>Item is added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Validate user can search for items 
+2.Validate user can choose from options
+3. Validate user can add items
+4. Validate user can update items quantity
+5. Validate user can delete items </t>
+  </si>
+  <si>
+    <t>Validate user can update items quantity</t>
+  </si>
+  <si>
+    <t>1. Choose an already selected item
+2. Click on + to increase the quantity</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Item quantity should be increased</t>
+  </si>
+  <si>
+    <t>1. Choose an already selected item
+2. Click on - to decrease the quantity</t>
+  </si>
+  <si>
+    <t>Item quantity should be decreased</t>
+  </si>
+  <si>
+    <t>Item quantity is increased</t>
+  </si>
+  <si>
+    <t>Item quantity is decreased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate user can delete items </t>
+  </si>
+  <si>
+    <t>1. Item is added already</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Item is added already
+</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_21</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_22</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_23</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_24</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_25</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_26</t>
+  </si>
+  <si>
+    <t>1. Choose an already selected item
+2. Click on - to decrease the quantity until it is 0</t>
+  </si>
+  <si>
+    <t>Item quantity should be 0 and item should not be selected anymore</t>
+  </si>
+  <si>
+    <t>Item quantity is 0 and item is not 
+selected anymore</t>
+  </si>
+  <si>
+    <t>1. Item is added</t>
+  </si>
+  <si>
+    <t>1. Kothanur</t>
+  </si>
+  <si>
+    <t>1. Koramangala 
+Food Street</t>
+  </si>
+  <si>
+    <t>1. Bangalore
+2. Koramangala 
+Food Street</t>
+  </si>
+  <si>
+    <t>1. Bangalore
+3. Kothanur</t>
+  </si>
+  <si>
+    <t>Validate user can select future date</t>
+  </si>
+  <si>
+    <t>1. Click on Continue
+2. Select a future date</t>
+  </si>
+  <si>
+    <t>2. 1st April</t>
+  </si>
+  <si>
+    <t>The Pickup date should be selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Pickup date is selected </t>
+  </si>
+  <si>
+    <t>Validate past date selection is restricted</t>
+  </si>
+  <si>
+    <t>1. Click on Continue
+2. Scroll to past dates</t>
+  </si>
+  <si>
+    <t>The date should not scroll to past dates</t>
+  </si>
+  <si>
+    <t>The date is not getting scrolled to 
+the past dates</t>
+  </si>
+  <si>
+    <t>1. Item is added
+2. Select Pickup date</t>
+  </si>
+  <si>
+    <t>1. select pickup slot
+2. select pickup time</t>
+  </si>
+  <si>
+    <t>1. Morning
+2. 8AM-9AM</t>
+  </si>
+  <si>
+    <t>The time is selected</t>
+  </si>
+  <si>
+    <t>The time should be selected</t>
+  </si>
+  <si>
+    <t>Validate valid time slot selection</t>
+  </si>
+  <si>
+    <t>Validate invalid time slot selection</t>
+  </si>
+  <si>
+    <t>1. select pickup slot
+2. select invalid pickup time</t>
+  </si>
+  <si>
+    <t>"Unavailable Please select another time" message should be displayed, the time slot should be disabled and continue button should be disabled</t>
+  </si>
+  <si>
+    <t>"Unavailable Please select another time" message is displayed, the time slot is disabled and continue button is disabled</t>
+  </si>
+  <si>
+    <t>Validate booking summary is displayed</t>
+  </si>
+  <si>
+    <t>1. Pickup date and pickup time is selected</t>
+  </si>
+  <si>
+    <t>Order Summary page should be displayed</t>
+  </si>
+  <si>
+    <t>Order Summary page is displayed</t>
+  </si>
+  <si>
+    <t>1. Click on Continue</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_27</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_28</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_29</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_30</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_31</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_32</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_33</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_34</t>
+  </si>
+  <si>
+    <t>Validate user can edit details</t>
+  </si>
+  <si>
+    <t>1. Order Summary is displayed</t>
+  </si>
+  <si>
+    <t>2. Cox Town</t>
+  </si>
+  <si>
+    <t>1. Click on edit in Movement Details section 
+2. Enter a valid pickup location
+3. Click on Save&amp;Continue</t>
+  </si>
+  <si>
+    <t>The pickup location should get changed</t>
+  </si>
+  <si>
+    <t>The pickup location is changed</t>
+  </si>
+  <si>
+    <t>1. Click on edit in Movement Details section 
+2. Enter a valid drop location
+3. Click on Save&amp;Continue</t>
+  </si>
+  <si>
+    <t>2. Koramangala</t>
+  </si>
+  <si>
+    <t>The drop location should get changed</t>
+  </si>
+  <si>
+    <t>The drop location is changed</t>
+  </si>
+  <si>
+    <t>1. Click on edit in Movement Details section 
+2. Enter a valid pickup location
+3. Enter a valid drop location
+4. Click on Save&amp;Continue</t>
+  </si>
+  <si>
+    <t>2. Koramangala
+3. Kothanur</t>
+  </si>
+  <si>
+    <t>The pickup location and drop location should get changed</t>
+  </si>
+  <si>
+    <t>The pickup location and drop location is changed</t>
+  </si>
+  <si>
+    <t>1. Click on edit in Movement Details section 
+2. Enter a invalid pickup location
+3. Enter a invalid drop location
+4. Click on Save&amp;Continue</t>
+  </si>
+  <si>
+    <t>2. dhcd
+3. sasa</t>
+  </si>
+  <si>
+    <t>"Please enter valid pickup and drop location" message should be displayed</t>
+  </si>
+  <si>
+    <t>"Please enter valid pickup and drop 
+location" message is displayed</t>
+  </si>
+  <si>
+    <t>1. Click on edit in Pickup date and time section
+2. Choose a valid date
+3. Choose a valid slot
+4. Click on Confirm</t>
+  </si>
+  <si>
+    <t>2. 24th March
+3. 3PM-4PM</t>
+  </si>
+  <si>
+    <t>The pickup date and slot time should be changed</t>
+  </si>
+  <si>
+    <t>The pickup date and slot time is changed</t>
+  </si>
+  <si>
+    <t>1. Click on edit in Pickup date and time section
+2. Choose a valid date
+3. Choose a invalid slot
+4. Click on Confirm</t>
+  </si>
+  <si>
+    <t>2. 24th March
+3. 9AM-10AM</t>
+  </si>
+  <si>
+    <t>1. Click on "Your added inventory" option
+2. Click on edit items
+3. Select an item
+4. Click on Continue</t>
+  </si>
+  <si>
+    <t>3. Center Table</t>
+  </si>
+  <si>
+    <t>Items list should increase and Order summary should change</t>
+  </si>
+  <si>
+    <t>Items list is increased and Order Summary is changed</t>
+  </si>
+  <si>
+    <t>Validate booking confirmation</t>
+  </si>
+  <si>
+    <t>1. Click on Confirm Booking</t>
+  </si>
+  <si>
+    <t>Navigates to Payment Page</t>
+  </si>
+  <si>
+    <t>Should navigate to Payment Page</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_35</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_36</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_37</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_38</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_39</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_40</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_41</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_42</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_43</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_44</t>
+  </si>
+  <si>
+    <t>1. Confirmed booking</t>
+  </si>
+  <si>
+    <t>Validate payment with valid method</t>
+  </si>
+  <si>
+    <t>1. Select a payment method</t>
+  </si>
+  <si>
+    <t>Displays the QR</t>
+  </si>
+  <si>
+    <t>Should display the QR</t>
+  </si>
+  <si>
+    <t>1. UPI</t>
+  </si>
+  <si>
+    <t>1. Credit or Debit card</t>
+  </si>
+  <si>
+    <t>The fields for details should get opened</t>
+  </si>
+  <si>
+    <t>The fields for details is opened</t>
+  </si>
+  <si>
+    <t>1. Select a payment method
+2. Click on Add New Cards</t>
+  </si>
+  <si>
+    <t>1. Select a payment method
+2. Select a Bank
+3. Click on Make Payment</t>
+  </si>
+  <si>
+    <t>1. Net Banking
+2. SBI</t>
+  </si>
+  <si>
+    <t>Should Navigate to Bank Payment Page</t>
+  </si>
+  <si>
+    <t>Navigates to Bank Payment Page</t>
+  </si>
+  <si>
+    <t>Validate successful payment flow</t>
+  </si>
+  <si>
+    <t>1. QR is scanned for UPI
+2. Money is paid</t>
+  </si>
+  <si>
+    <t>"Payment successful" message should be displayed</t>
+  </si>
+  <si>
+    <t>"Payment successful" message is displayed</t>
+  </si>
+  <si>
+    <t>1. 6757345678123479
+2. 12/35
+3. 478
+4. Latika Pal</t>
+  </si>
+  <si>
+    <t>1. Select a payment method as UPI</t>
+  </si>
+  <si>
+    <t>1. Enter details in the Bank Payment gateway
+2. Click on Pay</t>
+  </si>
+  <si>
+    <t>1. Enter valid Card Number
+2.Enter valid Validity Date
+3. Enter valid CVV
+4. Enter valid Name
+5. Click on Pay</t>
+  </si>
+  <si>
+    <t>1. Selected a payment method as UPI</t>
+  </si>
+  <si>
+    <t>1. Selected a payment method as Credit and Debit Card</t>
+  </si>
+  <si>
+    <t>1. Selected a payment method as Net Banking</t>
+  </si>
+  <si>
+    <t>Validate failed payment handling</t>
+  </si>
+  <si>
+    <t>1. QR is scanned for UPI
+2. Timer got up but unable to pay</t>
+  </si>
+  <si>
+    <t>1. Enter invalid Card Number
+2.Enter valid Validity Date
+3. Enter valid CVV
+4. Enter valid Name
+5. Click on Pay</t>
+  </si>
+  <si>
+    <t>1. AB12345
+2. 12/35
+3. 478
+4. Latika Pal</t>
+  </si>
+  <si>
+    <t>1. Enter wrong details in the Bank Payment gateway
+2. Click on Pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Payment failed" message should be displayed and order should not be confirmed </t>
+  </si>
+  <si>
+    <t>"Payment failed" message is displayed and order is not confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate user can enter valid pickup and drop
+ location </t>
+  </si>
+  <si>
+    <t>1. Select a valid city
+2. Enter a valid pickup location
+3. Enter a valid drop location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter a valid pickup location
+</t>
+  </si>
+  <si>
+    <t>1. Bangalore
+2. Koramangala 
+Food Street
+3. Kothanur</t>
+  </si>
+  <si>
+    <t>The locations should be selected</t>
+  </si>
+  <si>
+    <t>The locations are selected</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Validate navigation to Packers and Movers Page</t>
+  </si>
+  <si>
+    <t>1. Click on Menu  Option
+2. Click on "Packers and Movers" Option</t>
+  </si>
+  <si>
+    <t>Should navigate to Packers and 
+Movers page</t>
+  </si>
+  <si>
+    <t>Navigates to Packers and Movers 
+page</t>
+  </si>
+  <si>
+    <t>Defect Id.</t>
+  </si>
+  <si>
+    <t>Module name</t>
+  </si>
+  <si>
+    <t>Defect Summary</t>
+  </si>
+  <si>
+    <t>Defect Priority</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Packers and Movers</t>
+  </si>
+  <si>
+    <t>BR_ID</t>
+  </si>
+  <si>
+    <t>TR_ID</t>
+  </si>
+  <si>
+    <t>TS_ID</t>
+  </si>
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>DR_ID</t>
+  </si>
+  <si>
+    <t>DR_NoBroker_01</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_01</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_02</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_03</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_02</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_07</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_06</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_05</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_04</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_01</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_07</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_06</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_05</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_04</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_03</t>
+  </si>
+  <si>
+    <t>1. Choose a category
+2.Choose a subcategory and click on it
+3. Choose any item and click on + button to add the item</t>
+  </si>
+  <si>
+    <t>1. Bedroom
+2. Bed
+3. King Size Bed - With Storage</t>
+  </si>
+  <si>
+    <t>"Carton is added" message should be displayed</t>
+  </si>
+  <si>
+    <t>1. Choose a category
+2.Choose a subcategory and select one
+3. Enter the number of items to be added</t>
+  </si>
+  <si>
+    <t>1. Cartons
+2. Self Carton-Large
+3. 5</t>
+  </si>
+  <si>
+    <t>"You have added 0 cartons" message 
+is displayed</t>
+  </si>
+  <si>
+    <t>TEST EXECUTION SUMMARY</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Total Passed</t>
+  </si>
+  <si>
+    <t>Total Failed</t>
+  </si>
+  <si>
+    <t>Total Executed</t>
+  </si>
+  <si>
+    <t>Pass Percentage</t>
+  </si>
+  <si>
+    <t>Fail Percentage</t>
+  </si>
+  <si>
+    <t>Complition Percentage</t>
+  </si>
+  <si>
+    <t>Item addition shows incorrect quantity message (“0 cartons”) 
+despite adding items, indicating failure in inventory count update functionality.</t>
+  </si>
+  <si>
+    <t>NoBroker</t>
+  </si>
+  <si>
+    <t>Packers &amp; Movers - Navigation</t>
+  </si>
+  <si>
+    <t>Packers &amp; Movers - Location Input</t>
+  </si>
+  <si>
+    <t>Packers &amp; Movers - Shifting Type</t>
+  </si>
+  <si>
+    <t>Packers &amp; Movers - Inventory Management</t>
+  </si>
+  <si>
+    <t>Packers &amp; Movers - Slot Booking</t>
+  </si>
+  <si>
+    <t>Packers &amp; Movers - Booking Confirmation</t>
+  </si>
+  <si>
+    <t>Packers &amp; Movers - Payment Functionality</t>
+  </si>
+  <si>
+    <t>Packers &amp; Movers</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>1. Select an invalid city
+2. Enter an invalid pickup location
+3. Enter an invalid drop location</t>
+  </si>
+  <si>
+    <t>"This route is currently not 
+serviceable" message should be
+displayed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,8 +1379,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -495,8 +1471,74 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBDE8D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -519,11 +1561,101 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -543,9 +1675,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -553,16 +1682,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -570,15 +1690,204 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{F0AEA88B-52D9-48EC-A6A3-B22B5F2692E7}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFEBDE8D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -914,656 +2223,656 @@
   <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.54296875" style="21" customWidth="1"/>
-    <col min="2" max="2" width="60.81640625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="11" style="21" customWidth="1"/>
-    <col min="4" max="11" width="8.7265625" style="17"/>
+    <col min="1" max="1" width="27.54296875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="60.81640625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="11" style="17" customWidth="1"/>
+    <col min="4" max="11" width="8.7265625" style="14"/>
     <col min="12" max="15" width="8.7265625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
       <c r="L1" s="9"/>
       <c r="M1" s="9"/>
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
     </row>
     <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8"/>
       <c r="N2" s="8"/>
       <c r="O2" s="8"/>
     </row>
     <row r="3" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
     </row>
     <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="B4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
     <row r="5" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
+      <c r="B5" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
       <c r="L5" s="8"/>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="A6" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
+      <c r="A7" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
     <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
     </row>
     <row r="10" spans="1:15" s="4" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
+      <c r="A10" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
     </row>
     <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="20" t="s">
+      <c r="A11" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
     <row r="12" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
     </row>
     <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
     </row>
     <row r="14" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="17" t="s">
+      <c r="A14" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
     </row>
     <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="A15" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
     </row>
     <row r="16" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="17" t="s">
+      <c r="A18" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
     </row>
     <row r="19" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
+      <c r="A19" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
     </row>
-    <row r="20" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
+    <row r="20" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
     </row>
-    <row r="21" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
+    <row r="21" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
     </row>
     <row r="22" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
+      <c r="A22" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
     </row>
-    <row r="23" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
+    <row r="23" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
     </row>
-    <row r="24" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
+    <row r="24" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
     </row>
     <row r="25" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
+      <c r="A25" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
     </row>
     <row r="26" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
+      <c r="A26" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
     </row>
     <row r="27" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
+      <c r="A27" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
     </row>
     <row r="28" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="20" t="s">
+      <c r="A28" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
+      <c r="B29" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
+      <c r="B30" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
@@ -1589,164 +2898,164 @@
     <col min="6" max="6" width="38.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="14" t="s">
+    </row>
+    <row r="2" spans="1:6" s="64" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A2" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="62" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" s="17" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="15">
+      <c r="E2" s="61">
         <v>3</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>98</v>
+      <c r="F2" s="63" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" s="10">
         <v>4</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="64" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="61">
+        <v>3</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="D5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="10">
+        <v>5</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="64" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="61">
         <v>3</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="10">
-        <v>4</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="10">
-        <v>3</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>55</v>
+      <c r="F6" s="63" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" s="10">
         <v>3</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="64" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="62" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="D8" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="61">
         <v>3</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>57</v>
+      <c r="F8" s="63" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1757,141 +3066,3050 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A50FB2-968D-487A-921E-670711AE7276}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
     <col min="2" max="2" width="39.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.6328125" customWidth="1"/>
+    <col min="5" max="5" width="28.08984375" customWidth="1"/>
     <col min="6" max="6" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.81640625" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="29.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14.6328125" style="30" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.1796875" customWidth="1"/>
     <col min="11" max="11" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.7265625" customWidth="1"/>
     <col min="13" max="13" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="26" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:13" s="56" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="E1" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="F1" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="G1" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="H1" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="J1" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="26" t="s">
+      <c r="K1" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="26" t="s">
+    </row>
+    <row r="2" spans="1:13" s="57" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="B2" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2" s="57" t="s">
+        <v>328</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>329</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>331</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="25" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="D3" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="25" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="25" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="25" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="25" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="25" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>389</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="25" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="32" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="31" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C14" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="31" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="H4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>110</v>
-      </c>
+      <c r="C15" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="31" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="36" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="36" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="38" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="38" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>365</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="I20" s="27" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="38" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A21" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="I21" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="38" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A22" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H22" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="38" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A23" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="I23" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="43" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="B24" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F24" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="G24" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="43" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="G25" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="43" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="G26" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>227</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="43" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="G27" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="H27" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="46" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="44" t="s">
+        <v>239</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>234</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="F28" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="46" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A29" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="B29" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>250</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="H29" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="46" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A30" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="F30" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="G30" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="H30" s="44" t="s">
+        <v>256</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="46" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="44" t="s">
+        <v>242</v>
+      </c>
+      <c r="B31" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E31" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="F31" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="G31" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="H31" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="I31" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="46" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="44" t="s">
+        <v>243</v>
+      </c>
+      <c r="B32" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="G32" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="H32" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="I32" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="46" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E33" s="47" t="s">
+        <v>265</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="H33" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="46" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E34" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>270</v>
+      </c>
+      <c r="G34" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="H34" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="46" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="B35" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="F35" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="G35" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="49" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="B36" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36" s="48" t="s">
+        <v>275</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="F36" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="G36" s="50" t="s">
+        <v>278</v>
+      </c>
+      <c r="H36" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="I36" s="34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="53" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="B37" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>290</v>
+      </c>
+      <c r="E37" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="F37" s="54" t="s">
+        <v>294</v>
+      </c>
+      <c r="G37" s="54" t="s">
+        <v>293</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>292</v>
+      </c>
+      <c r="I37" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="53" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A38" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="B38" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="D38" s="52" t="s">
+        <v>290</v>
+      </c>
+      <c r="E38" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="F38" s="54" t="s">
+        <v>295</v>
+      </c>
+      <c r="G38" s="54" t="s">
+        <v>296</v>
+      </c>
+      <c r="H38" s="54" t="s">
+        <v>297</v>
+      </c>
+      <c r="I38" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="53" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="52" t="s">
+        <v>282</v>
+      </c>
+      <c r="B39" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="D39" s="52" t="s">
+        <v>290</v>
+      </c>
+      <c r="E39" s="55" t="s">
+        <v>299</v>
+      </c>
+      <c r="F39" s="54" t="s">
+        <v>300</v>
+      </c>
+      <c r="G39" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="H39" s="54" t="s">
+        <v>302</v>
+      </c>
+      <c r="I39" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="53" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="52" t="s">
+        <v>283</v>
+      </c>
+      <c r="B40" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>311</v>
+      </c>
+      <c r="D40" s="52" t="s">
+        <v>303</v>
+      </c>
+      <c r="E40" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="F40" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="G40" s="54" t="s">
+        <v>305</v>
+      </c>
+      <c r="H40" s="54" t="s">
+        <v>306</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="53" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A41" s="52" t="s">
+        <v>284</v>
+      </c>
+      <c r="B41" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>312</v>
+      </c>
+      <c r="D41" s="52" t="s">
+        <v>303</v>
+      </c>
+      <c r="E41" s="54" t="s">
+        <v>310</v>
+      </c>
+      <c r="F41" s="55" t="s">
+        <v>307</v>
+      </c>
+      <c r="G41" s="54" t="s">
+        <v>305</v>
+      </c>
+      <c r="H41" s="54" t="s">
+        <v>306</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="53" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="B42" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="D42" s="52" t="s">
+        <v>303</v>
+      </c>
+      <c r="E42" s="55" t="s">
+        <v>309</v>
+      </c>
+      <c r="F42" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="G42" s="54" t="s">
+        <v>305</v>
+      </c>
+      <c r="H42" s="54" t="s">
+        <v>306</v>
+      </c>
+      <c r="I42" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="53" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="52" t="s">
+        <v>286</v>
+      </c>
+      <c r="B43" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>308</v>
+      </c>
+      <c r="D43" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="E43" s="55" t="s">
+        <v>315</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="G43" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="H43" s="54" t="s">
+        <v>320</v>
+      </c>
+      <c r="I43" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="53" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="52" t="s">
+        <v>287</v>
+      </c>
+      <c r="B44" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>312</v>
+      </c>
+      <c r="D44" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="E44" s="55" t="s">
+        <v>316</v>
+      </c>
+      <c r="F44" s="54" t="s">
+        <v>317</v>
+      </c>
+      <c r="G44" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="H44" s="54" t="s">
+        <v>320</v>
+      </c>
+      <c r="I44" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="53" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="52" t="s">
+        <v>288</v>
+      </c>
+      <c r="B45" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="D45" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="E45" s="55" t="s">
+        <v>318</v>
+      </c>
+      <c r="F45" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="G45" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="H45" s="54" t="s">
+        <v>320</v>
+      </c>
+      <c r="I45" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="24"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="24"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="24"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="24"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="24"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="24"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="24"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="24"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019EA2C4-0BE4-44C3-A31A-C846AB1CDDA0}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" customWidth="1"/>
+    <col min="3" max="3" width="52.1796875" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="68" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>336</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="89" customFormat="1" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="92" t="s">
+        <v>347</v>
+      </c>
+      <c r="B2" s="90" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2" s="91" t="s">
+        <v>378</v>
+      </c>
+      <c r="D2" s="92" t="s">
+        <v>338</v>
+      </c>
+      <c r="E2" s="93"/>
+      <c r="F2" s="92" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.35">
+      <c r="A5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B97AD3BE-07CF-465A-9322-C7B5D44A83AA}">
+  <dimension ref="A1:F518"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.36328125" customWidth="1"/>
+    <col min="2" max="2" width="15.90625" customWidth="1"/>
+    <col min="3" max="3" width="29.453125" customWidth="1"/>
+    <col min="4" max="4" width="34.08984375" style="73" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="33.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="66" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1" s="75" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1" s="74" t="s">
+        <v>344</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>345</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="69" t="s">
+        <v>348</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>356</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="69" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D4" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D5" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D6" s="73" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D7" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D8" s="73" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D9" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D10" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D11" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="78"/>
+      <c r="D12" s="73" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="78"/>
+      <c r="D13" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="69" t="s">
+        <v>361</v>
+      </c>
+      <c r="B14" s="69" t="s">
+        <v>350</v>
+      </c>
+      <c r="C14" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D15" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D16" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="B17" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D18" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D19" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D20" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D21" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D22" s="73" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D23" s="73" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="B24" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="C24" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D25" s="73" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D26" s="73" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D27" s="73" t="s">
+        <v>206</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="69" t="s">
+        <v>358</v>
+      </c>
+      <c r="B28" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="C28" s="69" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="73" t="s">
+        <v>239</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D29" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D30" s="73" t="s">
+        <v>241</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D31" s="73" t="s">
+        <v>242</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D32" s="73" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D33" s="73" t="s">
+        <v>244</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D34" s="73" t="s">
+        <v>245</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D35" s="73" t="s">
+        <v>246</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D36" s="73" t="s">
+        <v>279</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="B37" s="69" t="s">
+        <v>352</v>
+      </c>
+      <c r="C37" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="73" t="s">
+        <v>280</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D38" s="73" t="s">
+        <v>281</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D39" s="73" t="s">
+        <v>282</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D40" s="73" t="s">
+        <v>283</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D41" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D42" s="73" t="s">
+        <v>285</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F42" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D43" s="73" t="s">
+        <v>286</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D44" s="73" t="s">
+        <v>287</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D45" s="80" t="s">
+        <v>288</v>
+      </c>
+      <c r="E45" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="F45" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="49" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="50" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="51" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="52" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="53" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="54" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="55" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="56" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="57" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="58" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="59" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="60" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="61" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="62" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="63" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="64" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="65" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="66" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="67" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="68" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="69" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="70" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="71" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="72" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="73" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="74" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="75" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="76" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="77" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="78" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="79" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="80" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="81" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="82" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="83" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="84" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="85" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="86" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="87" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="89" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="90" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="91" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="92" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="93" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="94" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="95" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="96" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="97" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="98" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="99" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="100" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="101" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="102" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="103" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="104" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="105" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="106" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="107" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="108" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="109" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="110" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="111" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="112" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="113" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="114" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="115" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="116" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="117" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="118" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="119" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="120" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="121" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="122" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="123" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="124" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="125" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="126" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="127" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="128" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="129" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="130" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="131" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="132" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="133" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="134" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="135" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="136" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="137" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="138" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="139" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="140" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="141" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="142" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="143" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="144" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="145" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="146" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="147" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="148" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="149" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="150" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="151" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="152" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="153" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="154" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="155" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="156" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="157" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="158" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="159" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="160" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="161" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="162" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="163" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="164" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="165" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="166" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="167" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="168" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="169" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="170" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="171" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="172" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="173" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="174" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="175" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="176" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="177" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="178" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="179" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="180" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="181" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="182" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="183" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="184" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="185" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="186" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="187" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="188" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="189" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="190" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="191" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="192" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="193" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="194" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="195" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="196" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="197" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="198" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="199" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="200" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="201" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="202" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="203" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="204" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="205" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="206" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="207" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="208" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="209" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="210" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="211" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="212" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="213" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="214" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="215" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="216" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="217" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="218" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="219" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="220" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="221" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="222" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="223" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="224" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="225" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="226" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="227" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="228" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="229" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="230" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="231" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="232" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="233" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="234" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="235" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="236" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="237" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="238" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="239" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="240" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="241" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="242" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="243" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="244" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="245" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="246" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="247" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="248" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="249" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="250" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="251" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="252" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="253" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="254" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="255" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="256" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="257" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="258" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="259" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="260" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="261" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="262" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="263" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="264" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="265" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="266" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="267" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="268" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="269" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="270" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="271" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="272" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="273" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="274" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="275" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="276" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="277" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="278" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="279" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="280" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="281" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="282" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="283" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="284" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="285" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="286" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="287" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="288" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="289" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="290" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="291" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="292" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="293" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="294" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="295" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="296" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="297" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="298" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="299" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="300" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="301" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="302" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="303" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="304" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="305" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="306" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="307" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="308" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="309" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="310" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="311" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="312" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="313" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="314" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="315" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="316" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="317" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="318" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="319" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="320" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="321" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="322" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="323" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="324" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="325" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="326" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="327" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="328" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="329" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="330" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="331" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="332" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="333" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="334" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="335" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="336" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="337" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="338" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="339" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="340" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="341" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="342" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="343" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="344" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="345" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="346" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="347" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="348" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="349" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="350" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="351" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="352" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="353" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="354" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="355" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="356" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="357" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="358" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="359" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="360" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="361" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="362" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="363" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="364" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="365" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="366" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="367" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="368" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="369" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="370" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="371" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="372" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="373" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="374" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="375" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="376" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="377" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="378" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="379" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="380" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="381" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="382" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="383" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="384" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="385" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="386" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="387" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="388" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="389" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="390" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="391" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="392" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="393" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="394" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="395" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="396" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="397" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="398" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="399" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="400" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="401" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="402" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="403" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="404" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="405" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="406" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="407" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="408" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="409" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="410" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="411" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="412" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="413" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="414" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="415" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="416" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="417" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="418" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="419" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="420" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="421" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="422" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="423" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="424" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="425" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="426" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="427" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="428" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="429" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="430" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="431" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="432" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="433" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="434" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="435" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="436" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="437" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="438" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="439" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="440" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="441" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="442" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="443" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="444" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="445" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="446" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="447" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="448" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="449" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="450" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="451" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="452" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="453" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="454" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="455" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="456" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="457" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="458" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="459" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="460" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="461" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="462" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="463" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="464" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="465" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="466" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="467" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="468" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="469" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="470" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="471" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="472" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="473" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="474" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="475" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="476" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="477" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="478" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="479" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="480" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="481" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="482" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="483" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="484" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="485" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="486" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="487" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="488" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="489" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="490" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="491" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="492" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="493" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="494" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="495" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="496" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="497" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="498" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="499" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="500" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="501" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="502" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="503" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="504" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="505" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="506" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="507" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="508" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="509" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="510" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="511" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="512" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="513" spans="4:5" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="514" spans="4:5" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="515" spans="4:5" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="516" spans="4:5" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="517" spans="4:5" s="14" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="518" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D518" s="82"/>
+      <c r="E518" s="83"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F40CC4-B79E-4DCD-9D35-127F7E878291}">
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.90625" customWidth="1"/>
+    <col min="2" max="2" width="36.26953125" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="33" width="8.7265625" style="14"/>
+    <col min="34" max="34" width="8.7265625" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" s="17" customFormat="1" ht="32.5" x14ac:dyDescent="0.7">
+      <c r="A1" s="84" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+    </row>
+    <row r="2" spans="1:34" s="17" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="66" t="s">
+        <v>369</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>371</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>372</v>
+      </c>
+      <c r="E2" s="66" t="s">
+        <v>373</v>
+      </c>
+      <c r="F2" s="66" t="s">
+        <v>374</v>
+      </c>
+      <c r="G2" s="66" t="s">
+        <v>375</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>376</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>377</v>
+      </c>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+    </row>
+    <row r="3" spans="1:34" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="86" t="s">
+        <v>379</v>
+      </c>
+      <c r="B3" s="70" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" s="71">
+        <v>1</v>
+      </c>
+      <c r="D3" s="71">
+        <v>1</v>
+      </c>
+      <c r="E3" s="71">
+        <v>0</v>
+      </c>
+      <c r="F3" s="71">
+        <v>2</v>
+      </c>
+      <c r="G3" s="72">
+        <v>1</v>
+      </c>
+      <c r="H3" s="72">
+        <v>0</v>
+      </c>
+      <c r="I3" s="76">
+        <v>1</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+    </row>
+    <row r="4" spans="1:34" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="87"/>
+      <c r="B4" s="70" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4" s="71">
+        <v>11</v>
+      </c>
+      <c r="D4" s="71">
+        <v>11</v>
+      </c>
+      <c r="E4" s="71">
+        <v>0</v>
+      </c>
+      <c r="F4" s="71">
+        <v>11</v>
+      </c>
+      <c r="G4" s="72">
+        <v>1</v>
+      </c>
+      <c r="H4" s="72">
+        <v>0</v>
+      </c>
+      <c r="I4" s="76">
+        <v>1</v>
+      </c>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="14"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="14"/>
+    </row>
+    <row r="5" spans="1:34" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="87"/>
+      <c r="B5" s="70" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="70">
+        <v>3</v>
+      </c>
+      <c r="D5" s="70">
+        <v>3</v>
+      </c>
+      <c r="E5" s="70">
+        <v>0</v>
+      </c>
+      <c r="F5" s="70">
+        <v>3</v>
+      </c>
+      <c r="G5" s="72">
+        <v>1</v>
+      </c>
+      <c r="H5" s="72">
+        <v>0</v>
+      </c>
+      <c r="I5" s="77">
+        <v>1</v>
+      </c>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+    </row>
+    <row r="6" spans="1:34" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="87"/>
+      <c r="B6" s="70" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6" s="70">
+        <v>7</v>
+      </c>
+      <c r="D6" s="70">
+        <v>6</v>
+      </c>
+      <c r="E6" s="70">
+        <v>1</v>
+      </c>
+      <c r="F6" s="70">
+        <v>7</v>
+      </c>
+      <c r="G6" s="72">
+        <v>0.86</v>
+      </c>
+      <c r="H6" s="72">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I6" s="77">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+    </row>
+    <row r="7" spans="1:34" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="87"/>
+      <c r="B7" s="70" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" s="70">
+        <v>4</v>
+      </c>
+      <c r="D7" s="70">
+        <v>4</v>
+      </c>
+      <c r="E7" s="70">
+        <v>0</v>
+      </c>
+      <c r="F7" s="70">
+        <v>4</v>
+      </c>
+      <c r="G7" s="72">
+        <v>1</v>
+      </c>
+      <c r="H7" s="72">
+        <v>0</v>
+      </c>
+      <c r="I7" s="77">
+        <v>1</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+    </row>
+    <row r="8" spans="1:34" s="70" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="87"/>
+      <c r="B8" s="70" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" s="70">
+        <v>9</v>
+      </c>
+      <c r="D8" s="70">
+        <v>9</v>
+      </c>
+      <c r="E8" s="70">
+        <v>0</v>
+      </c>
+      <c r="F8" s="70">
+        <v>9</v>
+      </c>
+      <c r="G8" s="72">
+        <v>1</v>
+      </c>
+      <c r="H8" s="72">
+        <v>0</v>
+      </c>
+      <c r="I8" s="77">
+        <v>1</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+    </row>
+    <row r="9" spans="1:34" s="96" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="88"/>
+      <c r="B9" s="96" t="s">
+        <v>386</v>
+      </c>
+      <c r="C9" s="96">
+        <v>9</v>
+      </c>
+      <c r="D9" s="96">
+        <v>9</v>
+      </c>
+      <c r="E9" s="96">
+        <v>0</v>
+      </c>
+      <c r="F9" s="96">
+        <v>9</v>
+      </c>
+      <c r="G9" s="97">
+        <v>1</v>
+      </c>
+      <c r="H9" s="97">
+        <v>0</v>
+      </c>
+      <c r="I9" s="98">
+        <v>1</v>
+      </c>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="99"/>
+      <c r="S9" s="99"/>
+      <c r="T9" s="99"/>
+      <c r="U9" s="99"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="99"/>
+      <c r="X9" s="99"/>
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="99"/>
+      <c r="AC9" s="99"/>
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
+      <c r="AF9" s="99"/>
+      <c r="AG9" s="99"/>
+    </row>
+    <row r="10" spans="1:34" s="95" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="102" t="s">
+        <v>388</v>
+      </c>
+      <c r="B10" s="101" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10" s="103">
+        <v>44</v>
+      </c>
+      <c r="D10" s="103">
+        <v>42</v>
+      </c>
+      <c r="E10" s="103">
+        <v>2</v>
+      </c>
+      <c r="F10" s="103">
+        <v>44</v>
+      </c>
+      <c r="G10" s="104">
+        <v>0.97</v>
+      </c>
+      <c r="H10" s="104">
+        <v>0.03</v>
+      </c>
+      <c r="I10" s="104">
+        <v>1</v>
+      </c>
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="94"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="94"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
+      <c r="T10" s="94"/>
+      <c r="U10" s="94"/>
+      <c r="V10" s="94"/>
+      <c r="W10" s="94"/>
+      <c r="X10" s="94"/>
+      <c r="Y10" s="94"/>
+      <c r="Z10" s="94"/>
+      <c r="AA10" s="94"/>
+      <c r="AB10" s="94"/>
+      <c r="AC10" s="94"/>
+      <c r="AD10" s="94"/>
+      <c r="AE10" s="94"/>
+      <c r="AF10" s="94"/>
+      <c r="AG10" s="94"/>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
+      <c r="N11" s="100"/>
+      <c r="O11" s="100"/>
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="100"/>
+      <c r="S11" s="100"/>
+      <c r="T11" s="100"/>
+      <c r="U11" s="100"/>
+      <c r="V11" s="100"/>
+      <c r="W11" s="100"/>
+      <c r="X11" s="100"/>
+      <c r="Y11" s="100"/>
+      <c r="Z11" s="100"/>
+      <c r="AA11" s="100"/>
+      <c r="AB11" s="100"/>
+      <c r="AC11" s="100"/>
+      <c r="AD11" s="100"/>
+      <c r="AE11" s="100"/>
+      <c r="AF11" s="100"/>
+      <c r="AG11" s="100"/>
+      <c r="AH11" s="83"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>